--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D7E2610-1E18-4C76-A879-5B98457BA6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7EBF4B-126B-4B63-B893-201D0CA1E12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -557,10 +557,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Assets/Model/Prefab/2221.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -577,10 +573,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,2,21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>消耗道具(1000人份)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -802,6 +794,14 @@
   </si>
   <si>
     <t>50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,19,20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,19,20,21</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1299,38 +1299,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AJ71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.7265625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.75" style="2" customWidth="1"/>
+    <col min="7" max="8" width="7.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="20.7265625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="24.453125" style="2" customWidth="1"/>
-    <col min="18" max="19" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.7265625" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="16.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="20.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="24.5" style="2" customWidth="1"/>
+    <col min="18" max="19" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="19.75" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="16.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="94.90625" style="2" customWidth="1"/>
-    <col min="30" max="30" width="33.6328125" style="2" customWidth="1"/>
-    <col min="31" max="31" width="55.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="45.08984375" style="2" customWidth="1"/>
-    <col min="33" max="33" width="41.90625" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="94.875" style="2" customWidth="1"/>
+    <col min="30" max="30" width="33.625" style="2" customWidth="1"/>
+    <col min="31" max="31" width="55.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="45.125" style="2" customWidth="1"/>
+    <col min="33" max="33" width="41.875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.75" style="2" bestFit="1" customWidth="1"/>
     <col min="35" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1367,7 +1367,7 @@
         <v>64</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O1" s="8" t="s">
         <v>110</v>
@@ -1376,7 +1376,7 @@
         <v>109</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R1" s="13" t="s">
         <v>90</v>
@@ -1409,7 +1409,7 @@
         <v>49</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AC1" s="6" t="s">
         <v>62</v>
@@ -1430,7 +1430,7 @@
       <c r="AI1" s="8"/>
       <c r="AJ1" s="6"/>
     </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1470,7 +1470,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
     </row>
-    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1509,13 +1509,13 @@
         <v>73</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>108</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>96</v>
@@ -1551,10 +1551,10 @@
         <v>52</v>
       </c>
       <c r="AB3" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC3" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AD3" s="7"/>
       <c r="AE3" s="7" t="s">
@@ -1572,7 +1572,7 @@
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>55</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AC4" s="10" t="s">
         <v>63</v>
@@ -1676,18 +1676,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>65</v>
@@ -1737,13 +1737,13 @@
         <v>70</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AE5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AG5" s="2" t="s">
         <v>111</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AI5" s="4"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1792,10 +1792,10 @@
         <v>65</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
@@ -1818,16 +1818,16 @@
         <v>53</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AE6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>112</v>
@@ -1837,18 +1837,18 @@
       </c>
       <c r="AI6" s="4"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>117</v>
@@ -1875,10 +1875,10 @@
         <v>67</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
@@ -1901,16 +1901,16 @@
         <v>53</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AE7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>113</v>
@@ -1920,18 +1920,18 @@
       </c>
       <c r="AI7" s="4"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>120</v>
@@ -1958,10 +1958,10 @@
         <v>68</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
@@ -1987,13 +1987,13 @@
         <v>70</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AE8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>114</v>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AI8" s="4"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2041,10 +2041,10 @@
         <v>69</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
@@ -2067,19 +2067,19 @@
         <v>53</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AE9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>115</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AI9" s="4"/>
     </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2147,10 +2147,10 @@
         <v>53</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AE10" s="4" t="s">
         <v>39</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AI10" s="4"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2218,10 +2218,10 @@
         <v>53</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AE11" s="4" t="s">
         <v>40</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AI11" s="4"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>138</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G12" s="4">
         <v>70</v>
@@ -2262,10 +2262,10 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
@@ -2288,23 +2288,23 @@
         <v>54</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AE12" s="4" t="s">
         <v>36</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AI12" s="4"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>138</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>139</v>
+        <v>203</v>
       </c>
       <c r="G13" s="4">
         <v>90</v>
@@ -2335,16 +2335,16 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
@@ -2367,23 +2367,23 @@
         <v>54</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AE13" s="4" t="s">
         <v>37</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AI13" s="4"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>138</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="G14" s="4">
         <v>100</v>
@@ -2414,16 +2414,16 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
@@ -2446,37 +2446,37 @@
         <v>54</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AE14" s="4" t="s">
         <v>38</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AI14" s="4"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D15" s="4">
         <v>8</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G15" s="4">
         <v>90</v>
@@ -2496,13 +2496,13 @@
         <v>70</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
@@ -2525,40 +2525,40 @@
         <v>53</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE15" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AH15" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AI15" s="4"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D16" s="4">
         <v>8</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G16" s="4">
         <v>100</v>
@@ -2578,13 +2578,13 @@
         <v>70</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
@@ -2607,26 +2607,26 @@
         <v>53</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE16" s="4" t="s">
         <v>35</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AH16" s="2" t="s">
         <v>57</v>
       </c>
       <c r="AI16" s="4"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2637,10 +2637,10 @@
         <v>9</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G17" s="4">
         <v>80</v>
@@ -2649,7 +2649,7 @@
         <v>85</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J17" s="4">
         <v>18</v>
@@ -2660,13 +2660,13 @@
         <v>70</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
@@ -2689,26 +2689,26 @@
         <v>53</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE17" s="4" t="s">
         <v>33</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AH17" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AI17" s="4"/>
     </row>
-    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>9</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>121</v>
@@ -2742,13 +2742,13 @@
         <v>70</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
@@ -2771,26 +2771,26 @@
         <v>53</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC18" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE18" s="4" t="s">
         <v>34</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG18" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AH18" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AI18" s="4"/>
     </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2817,25 +2817,25 @@
         <v>126</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O19" s="4">
         <v>8</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>20</v>
       </c>
@@ -2862,25 +2862,25 @@
         <v>125</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>67</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O20" s="4">
         <v>13</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>23</v>
       </c>
@@ -2907,25 +2907,25 @@
         <v>125</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>67</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O21" s="4">
         <v>16</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>16</v>
       </c>
@@ -2952,25 +2952,25 @@
         <v>126</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O22" s="4">
         <v>9</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>17</v>
       </c>
@@ -2997,25 +2997,25 @@
         <v>125</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O23" s="4">
         <v>10</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>19</v>
       </c>
@@ -3042,25 +3042,25 @@
         <v>125</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O24" s="4">
         <v>12</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AC24" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="25" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>18</v>
       </c>
@@ -3093,22 +3093,22 @@
         <v>69</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O25" s="4">
         <v>11</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AD25" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>21</v>
       </c>
@@ -3141,27 +3141,27 @@
         <v>69</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O26" s="4">
         <v>14</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AD26" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>22</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D27" s="4">
         <v>5</v>
@@ -3189,22 +3189,22 @@
         <v>69</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O27" s="4">
         <v>15</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC27" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AD27" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3237,24 +3237,24 @@
         <v>69</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O28" s="4">
         <v>17</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AE28" s="4"/>
       <c r="AI28" s="4"/>
     </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3281,13 +3281,13 @@
         <v>125</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>68</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>121</v>
@@ -3296,12 +3296,12 @@
         <v>70</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AE29" s="4"/>
       <c r="AI29" s="4"/>
     </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3328,13 +3328,13 @@
         <v>125</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>68</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>122</v>
@@ -3343,10 +3343,10 @@
         <v>70</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3354,7 +3354,7 @@
       <c r="AE39" s="4"/>
       <c r="AI39" s="4"/>
     </row>
-    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3375,7 +3375,7 @@
       <c r="AE40" s="4"/>
       <c r="AI40" s="4"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3396,159 +3396,159 @@
       <c r="AE41" s="4"/>
       <c r="AI41" s="4"/>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AI42" s="4"/>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AI43" s="4"/>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AI44" s="4"/>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AI45" s="4"/>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AI46" s="4"/>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AI47" s="4"/>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AI48" s="4"/>
     </row>
-    <row r="49" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="AE49" s="4"/>
     </row>
-    <row r="50" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="AE50" s="4"/>
     </row>
-    <row r="51" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="AE51" s="4"/>
     </row>
-    <row r="52" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="AE52" s="4"/>
     </row>
-    <row r="53" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="AE53" s="4"/>
     </row>
-    <row r="54" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="AE54" s="4"/>
     </row>
-    <row r="55" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="AE55" s="4"/>
     </row>
-    <row r="56" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="AE56" s="4"/>
     </row>
-    <row r="57" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="AE57" s="4"/>
     </row>
-    <row r="58" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="AE58" s="4"/>
     </row>
-    <row r="59" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="AE59" s="4"/>
     </row>
-    <row r="60" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="AE60" s="4"/>
     </row>
-    <row r="61" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="AE61" s="4"/>
     </row>
-    <row r="62" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="AE62" s="4"/>
     </row>
-    <row r="63" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="AE63" s="4"/>
     </row>
-    <row r="64" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="AE64" s="4"/>
     </row>
-    <row r="65" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="AE65" s="4"/>
     </row>
-    <row r="66" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="AE66" s="4"/>
     </row>
-    <row r="67" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="AE67" s="4"/>
     </row>
-    <row r="68" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="AE68" s="4"/>
     </row>
-    <row r="69" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="AE69" s="4"/>
     </row>
-    <row r="70" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="AE70" s="4"/>
     </row>
-    <row r="71" spans="4:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
     </row>

--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7EBF4B-126B-4B63-B893-201D0CA1E12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BA6A7E-5E95-42C0-9DA6-0C8DB47D014A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="1140" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="206">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -802,6 +802,10 @@
   </si>
   <si>
     <t>1,2,19,20,21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Model/Prefab/p_toushi.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2783,7 +2787,7 @@
         <v>189</v>
       </c>
       <c r="AG18" s="2" t="s">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="AH18" s="2" t="s">
         <v>58</v>

--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BA6A7E-5E95-42C0-9DA6-0C8DB47D014A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF04A7C-C69D-4FD0-8571-B440F7CBD534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="1140" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="212">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -806,6 +806,29 @@
   </si>
   <si>
     <t>Assets/Model/Prefab/p_toushi.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moveSound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>62</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>63</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1302,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
-  <dimension ref="A1:AJ71"/>
+  <dimension ref="A1:AK71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
@@ -1331,10 +1354,11 @@
     <col min="32" max="32" width="45.125" style="2" customWidth="1"/>
     <col min="33" max="33" width="41.875" style="2" customWidth="1"/>
     <col min="34" max="34" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9" style="2"/>
+    <col min="35" max="36" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:37" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1432,9 +1456,10 @@
         <v>24</v>
       </c>
       <c r="AI1" s="8"/>
-      <c r="AJ1" s="6"/>
-    </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6"/>
+    </row>
+    <row r="2" spans="1:37" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1473,8 +1498,9 @@
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
-    </row>
-    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AK2" s="2"/>
+    </row>
+    <row r="3" spans="1:37" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1573,10 +1599,13 @@
       <c r="AH3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AI3" s="7"/>
+      <c r="AI3" s="7" t="s">
+        <v>206</v>
+      </c>
       <c r="AJ3" s="7"/>
-    </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AK3" s="7"/>
+    </row>
+    <row r="4" spans="1:37" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1679,8 +1708,11 @@
       <c r="AH4" s="15" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AI4" s="15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1755,9 +1787,12 @@
       <c r="AH5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AI5" s="4"/>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI5" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="AJ5" s="4"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1839,9 +1874,12 @@
       <c r="AH6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AI6" s="4"/>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="AJ6" s="4"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1922,9 +1960,12 @@
       <c r="AH7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AI7" s="4"/>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI7" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ7" s="4"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -2005,9 +2046,12 @@
       <c r="AH8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AI8" s="4"/>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI8" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ8" s="4"/>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2091,9 +2135,12 @@
       <c r="AH9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AI9" s="4"/>
-    </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AI9" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ9" s="4"/>
+    </row>
+    <row r="10" spans="1:37" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2162,9 +2209,12 @@
       <c r="AG10" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AI10" s="4"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI10" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ10" s="4"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2233,9 +2283,12 @@
       <c r="AG11" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="AI11" s="4"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI11" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ11" s="4"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2306,9 +2359,12 @@
       <c r="AG12" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="AI12" s="4"/>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI12" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ12" s="4"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2385,9 +2441,12 @@
       <c r="AG13" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="AI13" s="4"/>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI13" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ13" s="4"/>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2464,9 +2523,12 @@
       <c r="AG14" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AI14" s="4"/>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI14" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="AJ14" s="4"/>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2546,9 +2608,12 @@
       <c r="AH15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AI15" s="4"/>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AI15" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AJ15" s="4"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2628,9 +2693,12 @@
       <c r="AH16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AI16" s="4"/>
-    </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI16" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AJ16" s="4"/>
+    </row>
+    <row r="17" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2710,9 +2778,12 @@
       <c r="AH17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AI17" s="4"/>
-    </row>
-    <row r="18" spans="2:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AI17" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="AJ17" s="4"/>
+    </row>
+    <row r="18" spans="2:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2792,9 +2863,12 @@
       <c r="AH18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AI18" s="4"/>
-    </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI18" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="AJ18" s="4"/>
+    </row>
+    <row r="19" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2838,8 +2912,11 @@
       <c r="AC19" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI19" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>20</v>
       </c>
@@ -2883,8 +2960,11 @@
       <c r="AC20" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI20" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="21" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>23</v>
       </c>
@@ -2928,8 +3008,11 @@
       <c r="AC21" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI21" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="22" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>16</v>
       </c>
@@ -2973,8 +3056,11 @@
       <c r="AC22" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI22" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="23" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>17</v>
       </c>
@@ -3018,8 +3104,11 @@
       <c r="AC23" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI23" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="24" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>19</v>
       </c>
@@ -3063,8 +3152,11 @@
       <c r="AC24" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI24" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>18</v>
       </c>
@@ -3111,8 +3203,11 @@
       <c r="AD25" s="2" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI25" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="26" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>21</v>
       </c>
@@ -3159,8 +3254,11 @@
       <c r="AD26" s="2" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI26" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>22</v>
       </c>
@@ -3207,8 +3305,11 @@
       <c r="AD27" s="2" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI27" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="28" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3256,9 +3357,12 @@
         <v>170</v>
       </c>
       <c r="AE28" s="4"/>
-      <c r="AI28" s="4"/>
-    </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI28" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ28" s="4"/>
+    </row>
+    <row r="29" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3303,9 +3407,12 @@
         <v>190</v>
       </c>
       <c r="AE29" s="4"/>
-      <c r="AI29" s="4"/>
-    </row>
-    <row r="30" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI29" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ29" s="4"/>
+    </row>
+    <row r="30" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3349,16 +3456,19 @@
       <c r="AC30" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AI30" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="39" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="AE39" s="4"/>
-      <c r="AI39" s="4"/>
-    </row>
-    <row r="40" spans="2:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AJ39" s="4"/>
+    </row>
+    <row r="40" spans="2:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3377,9 +3487,9 @@
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
       <c r="AE40" s="4"/>
-      <c r="AI40" s="4"/>
-    </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AJ40" s="4"/>
+    </row>
+    <row r="41" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3398,49 +3508,49 @@
       <c r="V41" s="4"/>
       <c r="W41" s="4"/>
       <c r="AE41" s="4"/>
-      <c r="AI41" s="4"/>
-    </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AJ41" s="4"/>
+    </row>
+    <row r="42" spans="2:36" x14ac:dyDescent="0.15">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="AE42" s="4"/>
-      <c r="AI42" s="4"/>
-    </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AJ42" s="4"/>
+    </row>
+    <row r="43" spans="2:36" x14ac:dyDescent="0.15">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="AE43" s="4"/>
-      <c r="AI43" s="4"/>
-    </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AJ43" s="4"/>
+    </row>
+    <row r="44" spans="2:36" x14ac:dyDescent="0.15">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="AE44" s="4"/>
-      <c r="AI44" s="4"/>
-    </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AJ44" s="4"/>
+    </row>
+    <row r="45" spans="2:36" x14ac:dyDescent="0.15">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="AE45" s="4"/>
-      <c r="AI45" s="4"/>
-    </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AJ45" s="4"/>
+    </row>
+    <row r="46" spans="2:36" x14ac:dyDescent="0.15">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="AE46" s="4"/>
-      <c r="AI46" s="4"/>
-    </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AJ46" s="4"/>
+    </row>
+    <row r="47" spans="2:36" x14ac:dyDescent="0.15">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="AE47" s="4"/>
-      <c r="AI47" s="4"/>
-    </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AJ47" s="4"/>
+    </row>
+    <row r="48" spans="2:36" x14ac:dyDescent="0.15">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="AE48" s="4"/>
-      <c r="AI48" s="4"/>
+      <c r="AJ48" s="4"/>
     </row>
     <row r="49" spans="4:31" x14ac:dyDescent="0.15">
       <c r="D49" s="4"/>

--- a/Data/Export/Common/TroopType_部队类型.xlsx
+++ b/Data/Export/Common/TroopType_部队类型.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF04A7C-C69D-4FD0-8571-B440F7CBD534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TroopTypes" sheetId="36" r:id="rId1"/>
@@ -1326,39 +1326,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AK71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.75" style="2" customWidth="1"/>
-    <col min="7" max="8" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.7265625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="20.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="24.5" style="2" customWidth="1"/>
-    <col min="18" max="19" width="14.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.75" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="20.7265625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="24.453125" style="2" customWidth="1"/>
+    <col min="18" max="19" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="19.7265625" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="16.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="94.875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="33.625" style="2" customWidth="1"/>
-    <col min="31" max="31" width="55.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="45.125" style="2" customWidth="1"/>
-    <col min="33" max="33" width="41.875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="94.90625" style="2" customWidth="1"/>
+    <col min="30" max="30" width="33.6328125" style="2" customWidth="1"/>
+    <col min="31" max="31" width="55.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="45.08984375" style="2" customWidth="1"/>
+    <col min="33" max="33" width="41.90625" style="2" customWidth="1"/>
+    <col min="34" max="34" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="35" max="36" width="12" style="2" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:37" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -1459,7 +1459,7 @@
       <c r="AJ1" s="8"/>
       <c r="AK1" s="6"/>
     </row>
-    <row r="2" spans="1:37" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:37" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1500,7 +1500,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:37" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1605,7 +1605,7 @@
       <c r="AJ3" s="7"/>
       <c r="AK3" s="7"/>
     </row>
-    <row r="4" spans="1:37" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:37" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:37" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AJ5" s="4"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="AJ6" s="4"/>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="AJ7" s="4"/>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AJ8" s="4"/>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="AJ9" s="4"/>
     </row>
-    <row r="10" spans="1:37" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:37" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AJ10" s="4"/>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="AJ11" s="4"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AJ12" s="4"/>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AJ13" s="4"/>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AJ14" s="4"/>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AJ15" s="4"/>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AJ16" s="4"/>
     </row>
-    <row r="17" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AJ17" s="4"/>
     </row>
-    <row r="18" spans="2:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="AJ18" s="4"/>
     </row>
-    <row r="19" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>20</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="21" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>23</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="22" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>16</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="23" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>17</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="24" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>19</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="25" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>18</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="26" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>21</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>22</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="28" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="AJ28" s="4"/>
     </row>
-    <row r="29" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AJ29" s="4"/>
     </row>
-    <row r="30" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3468,7 +3468,7 @@
       <c r="AE39" s="4"/>
       <c r="AJ39" s="4"/>
     </row>
-    <row r="40" spans="2:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3489,7 +3489,7 @@
       <c r="AE40" s="4"/>
       <c r="AJ40" s="4"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3510,159 +3510,159 @@
       <c r="AE41" s="4"/>
       <c r="AJ41" s="4"/>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.25">
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AJ42" s="4"/>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.25">
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AJ43" s="4"/>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.25">
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AJ44" s="4"/>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.25">
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AJ45" s="4"/>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.25">
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="AE46" s="4"/>
       <c r="AJ46" s="4"/>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.25">
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="AE47" s="4"/>
       <c r="AJ47" s="4"/>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.25">
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="AE48" s="4"/>
       <c r="AJ48" s="4"/>
     </row>
-    <row r="49" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="49" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="AE49" s="4"/>
     </row>
-    <row r="50" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="50" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="AE50" s="4"/>
     </row>
-    <row r="51" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="51" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="AE51" s="4"/>
     </row>
-    <row r="52" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="52" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="AE52" s="4"/>
     </row>
-    <row r="53" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="53" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="AE53" s="4"/>
     </row>
-    <row r="54" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="54" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="AE54" s="4"/>
     </row>
-    <row r="55" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="55" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="AE55" s="4"/>
     </row>
-    <row r="56" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="56" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="AE56" s="4"/>
     </row>
-    <row r="57" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="57" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="AE57" s="4"/>
     </row>
-    <row r="58" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="58" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="AE58" s="4"/>
     </row>
-    <row r="59" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="59" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="AE59" s="4"/>
     </row>
-    <row r="60" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="60" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="AE60" s="4"/>
     </row>
-    <row r="61" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="61" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="AE61" s="4"/>
     </row>
-    <row r="62" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="62" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="AE62" s="4"/>
     </row>
-    <row r="63" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="63" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="AE63" s="4"/>
     </row>
-    <row r="64" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="64" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="AE64" s="4"/>
     </row>
-    <row r="65" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="65" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="AE65" s="4"/>
     </row>
-    <row r="66" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="66" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="AE66" s="4"/>
     </row>
-    <row r="67" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="67" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="AE67" s="4"/>
     </row>
-    <row r="68" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="68" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="AE68" s="4"/>
     </row>
-    <row r="69" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="69" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="AE69" s="4"/>
     </row>
-    <row r="70" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="70" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="AE70" s="4"/>
     </row>
-    <row r="71" spans="4:31" x14ac:dyDescent="0.15">
+    <row r="71" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
     </row>
